--- a/data/trans_orig/P36BPD03_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD03_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de verdura u hortalizas que consume al día en 2023</t>
+          <t>Población según el número de raciones de verdura u hortalizas que consume al día en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26792</t>
+          <t>27632</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50224</t>
+          <t>50356</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31937</t>
+          <t>32218</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50947</t>
+          <t>51017</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64187</t>
+          <t>64738</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93459</t>
+          <t>95163</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>107844</t>
+          <t>110122</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144282</t>
+          <t>145477</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>144984</t>
+          <t>145353</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>181586</t>
+          <t>182791</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>265241</t>
+          <t>266489</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>314943</t>
+          <t>318879</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>239993</t>
+          <t>238315</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>282971</t>
+          <t>281064</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>398056</t>
+          <t>397321</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>440513</t>
+          <t>439553</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>648167</t>
+          <t>647009</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>707758</t>
+          <t>708157</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,86%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73890</t>
+          <t>76186</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105721</t>
+          <t>107999</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>116398</t>
+          <t>114562</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>148725</t>
+          <t>146780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>200583</t>
+          <t>199171</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>247964</t>
+          <t>245205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91113</t>
+          <t>97007</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>170833</t>
+          <t>173139</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61502</t>
+          <t>60951</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>114155</t>
+          <t>112606</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>171086</t>
+          <t>173478</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>260066</t>
+          <t>267831</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>356116</t>
+          <t>382923</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>593382</t>
+          <t>589071</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>277827</t>
+          <t>297897</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>455717</t>
+          <t>459796</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>733509</t>
+          <t>742073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1015158</t>
+          <t>1023054</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1053377</t>
+          <t>1059903</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1531125</t>
+          <t>1481134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>808354</t>
+          <t>841685</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1253444</t>
+          <t>1255244</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2005718</t>
+          <t>2024413</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2645791</t>
+          <t>2647015</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,51%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>302201</t>
+          <t>309428</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>505176</t>
+          <t>505375</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>468704</t>
+          <t>465049</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1136493</t>
+          <t>1020771</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>880046</t>
+          <t>874698</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1611693</t>
+          <t>1607723</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11884</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>30591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14487</t>
+          <t>14354</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35850</t>
+          <t>35347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30455</t>
+          <t>30711</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59022</t>
+          <t>59737</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126385</t>
+          <t>127170</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>173267</t>
+          <t>174704</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>88163</t>
+          <t>85634</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>122508</t>
+          <t>121479</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>225512</t>
+          <t>223436</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>281905</t>
+          <t>281807</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>284860</t>
+          <t>286790</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>343051</t>
+          <t>340876</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>319757</t>
+          <t>318838</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>366294</t>
+          <t>363869</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>622904</t>
+          <t>620645</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>693728</t>
+          <t>695357</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,2%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139539</t>
+          <t>139720</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188351</t>
+          <t>186251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>172125</t>
+          <t>172970</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213503</t>
+          <t>215945</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>324488</t>
+          <t>323052</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>387335</t>
+          <t>382767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>142303</t>
+          <t>145050</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>230409</t>
+          <t>229437</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>118980</t>
+          <t>120472</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>175288</t>
+          <t>179790</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,47 +2487,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>340591</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>285225</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>387377</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>340591</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>290336</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>388097</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>622578</t>
+          <t>574040</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>868319</t>
+          <t>871995</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>538425</t>
+          <t>548551</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>722656</t>
+          <t>734410</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1237045</t>
+          <t>1252382</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1563814</t>
+          <t>1564589</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1622559</t>
+          <t>1631558</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2139797</t>
+          <t>2220652</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1489585</t>
+          <t>1545045</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2012269</t>
+          <t>2022238</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3363884</t>
+          <t>3360190</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4014648</t>
+          <t>3964875</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>55,86%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>541550</t>
+          <t>525293</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>769932</t>
+          <t>762306</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>789209</t>
+          <t>784381</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1482933</t>
+          <t>1469017</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1449691</t>
+          <t>1450848</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2119439</t>
+          <t>2227720</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD03_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD03_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>36938</t>
+          <t>38071</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27632</t>
+          <t>27382</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50356</t>
+          <t>50366</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40954</t>
+          <t>43570</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32218</t>
+          <t>34385</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51017</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>77892</t>
+          <t>81641</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64738</t>
+          <t>65707</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95163</t>
+          <t>97494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>126066</t>
+          <t>136148</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110122</t>
+          <t>117586</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145477</t>
+          <t>156365</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>162875</t>
+          <t>167931</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>145353</t>
+          <t>150525</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>182791</t>
+          <t>185211</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>288941</t>
+          <t>304079</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>266489</t>
+          <t>278819</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>318879</t>
+          <t>329909</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>260576</t>
+          <t>288864</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>238315</t>
+          <t>267747</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>281064</t>
+          <t>313227</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>418881</t>
+          <t>461868</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>397321</t>
+          <t>439281</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>439553</t>
+          <t>482671</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>679457</t>
+          <t>750732</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>647009</t>
+          <t>717314</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>708157</t>
+          <t>784459</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90616</t>
+          <t>114677</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76186</t>
+          <t>95456</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107999</t>
+          <t>135035</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>130765</t>
+          <t>146610</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>114562</t>
+          <t>130596</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>146780</t>
+          <t>165060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>221381</t>
+          <t>261287</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>199171</t>
+          <t>234954</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>245205</t>
+          <t>288744</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514197</t>
+          <t>577761</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514197</t>
+          <t>577761</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514197</t>
+          <t>577761</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>753475</t>
+          <t>819978</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>753475</t>
+          <t>819978</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>753475</t>
+          <t>819978</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1267672</t>
+          <t>1397739</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1267672</t>
+          <t>1397739</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1267672</t>
+          <t>1397739</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>134909</t>
+          <t>136891</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97007</t>
+          <t>112212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>173139</t>
+          <t>167191</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>85205</t>
+          <t>89324</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60951</t>
+          <t>72373</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>112606</t>
+          <t>110582</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>220114</t>
+          <t>226214</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>173478</t>
+          <t>195538</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>267831</t>
+          <t>265607</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>511293</t>
+          <t>519446</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>382923</t>
+          <t>478711</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>589071</t>
+          <t>563243</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,67 +1442,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>398115</t>
+          <t>435738</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>297897</t>
+          <t>400140</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>459796</t>
+          <t>469490</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>21,64%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1019</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>955184</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>903922</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>1017936</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>21,72%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>20,56%</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1019</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>909408</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>742073</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>1023054</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>20,1%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>16,4%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1205186</t>
+          <t>1077801</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1059903</t>
+          <t>1024997</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1481134</t>
+          <t>1135027</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1109094</t>
+          <t>1138915</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>841685</t>
+          <t>1098574</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1255244</t>
+          <t>1181279</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2314279</t>
+          <t>2216716</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2024413</t>
+          <t>2147206</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2647015</t>
+          <t>2291626</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>52,12%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>436394</t>
+          <t>493622</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>309428</t>
+          <t>449551</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>505375</t>
+          <t>540267</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>643544</t>
+          <t>505350</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>465049</t>
+          <t>471892</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1020771</t>
+          <t>543207</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1079938</t>
+          <t>998972</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>874698</t>
+          <t>941315</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1607723</t>
+          <t>1057523</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2287782</t>
+          <t>2227760</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2287782</t>
+          <t>2227760</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2287782</t>
+          <t>2227760</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2235958</t>
+          <t>2169327</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2235958</t>
+          <t>2169327</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2235958</t>
+          <t>2169327</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4523739</t>
+          <t>4397087</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4523739</t>
+          <t>4397087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4523739</t>
+          <t>4397087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>23189</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11688</t>
+          <t>14633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30591</t>
+          <t>35921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>16395</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35347</t>
+          <t>37484</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>42584</t>
+          <t>47822</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30711</t>
+          <t>35253</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59737</t>
+          <t>64475</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>149451</t>
+          <t>159179</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>127170</t>
+          <t>133103</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>174704</t>
+          <t>183866</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102872</t>
+          <t>110805</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>85634</t>
+          <t>93796</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>121479</t>
+          <t>129159</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>252324</t>
+          <t>269984</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>223436</t>
+          <t>237978</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>281807</t>
+          <t>298405</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>314135</t>
+          <t>344214</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>286790</t>
+          <t>315284</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>340876</t>
+          <t>374778</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>342374</t>
+          <t>377730</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>318838</t>
+          <t>352082</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>363869</t>
+          <t>402097</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>656509</t>
+          <t>721944</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>620645</t>
+          <t>684777</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>695357</t>
+          <t>761286</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,63%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>163036</t>
+          <t>185005</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139720</t>
+          <t>160059</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186251</t>
+          <t>211161</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>192633</t>
+          <t>221708</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>172970</t>
+          <t>198266</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215945</t>
+          <t>245657</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>355670</t>
+          <t>406713</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>323052</t>
+          <t>372001</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>382767</t>
+          <t>442923</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>191848</t>
+          <t>198151</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>145050</t>
+          <t>164772</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>229437</t>
+          <t>228317</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>148743</t>
+          <t>157527</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>120472</t>
+          <t>133503</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>179790</t>
+          <t>181646</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>340591</t>
+          <t>355678</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>285225</t>
+          <t>314763</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>387377</t>
+          <t>397500</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>786811</t>
+          <t>814774</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>574040</t>
+          <t>760635</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>871995</t>
+          <t>875141</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>663862</t>
+          <t>714474</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>548551</t>
+          <t>669934</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>734410</t>
+          <t>757750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1450673</t>
+          <t>1529248</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1252382</t>
+          <t>1467634</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1564589</t>
+          <t>1601766</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1779897</t>
+          <t>1710878</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1631558</t>
+          <t>1642280</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2220652</t>
+          <t>1775295</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1870349</t>
+          <t>1978514</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1545045</t>
+          <t>1927476</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2022238</t>
+          <t>2034640</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3650246</t>
+          <t>3689392</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3360190</t>
+          <t>3600089</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3964875</t>
+          <t>3772324</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>52,09%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>690046</t>
+          <t>793304</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>525293</t>
+          <t>735913</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>762306</t>
+          <t>849814</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>966942</t>
+          <t>873668</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>784381</t>
+          <t>829234</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1469017</t>
+          <t>920604</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1656988</t>
+          <t>1666972</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1450848</t>
+          <t>1603853</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2227720</t>
+          <t>1747431</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3448602</t>
+          <t>3517107</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3448602</t>
+          <t>3517107</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3448602</t>
+          <t>3517107</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3649896</t>
+          <t>3724183</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3649896</t>
+          <t>3724183</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3649896</t>
+          <t>3724183</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7098498</t>
+          <t>7241290</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7098498</t>
+          <t>7241290</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7098498</t>
+          <t>7241290</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
